--- a/backend/wp_templates/G/G13 公允价值变动收益.xlsx
+++ b/backend/wp_templates/G/G13 公允价值变动收益.xlsx
@@ -8256,7 +8256,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="93" t="str">
-        <f>IF(AND(G9=0,D7=0),"",IF(AND(G9=0,D7&gt;0),1,H7/G9))</f>
+        <f>IF(AND(G7=0,D7=0),"",IF(AND(G7=0,D7&gt;0),1,H7/G7))</f>
         <v/>
       </c>
       <c r="J7" s="94"/>
@@ -8574,7 +8574,7 @@
         <v>0</v>
       </c>
       <c r="G17" s="46">
-        <f>SUM(G9,G10,G13,G15:G16)</f>
+        <f>SUM(G7,G10,G13,G15:G16)</f>
         <v>0</v>
       </c>
       <c r="H17" s="46">
